--- a/大客户订购商品统计表_格式化模板.xlsx
+++ b/大客户订购商品统计表_格式化模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808972BE-729B-4BE3-A0DE-A78F15F0D327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B75E6C-A182-461F-838C-5472C0159FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大客户订购商品统计表" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -155,8 +155,16 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,6 +174,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -225,50 +239,50 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -761,20 +775,20 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="4.44140625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="6" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="4.44140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="6" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="10.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="6.88671875" style="10" customWidth="1"/>
-    <col min="11" max="11" width="9" style="10"/>
-    <col min="12" max="16384" width="9" style="11"/>
+    <col min="9" max="9" width="10.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="9" style="8"/>
+    <col min="12" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" ht="22.05" customHeight="1">
+    <row r="1" spans="1:11" s="4" customFormat="1" ht="22.05" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -783,39 +797,39 @@
         <v>12</v>
       </c>
       <c r="D1" s="3"/>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" s="5" customFormat="1" ht="24" customHeight="1">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="1"/>
@@ -823,52 +837,52 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="19.95" customHeight="1">
-      <c r="A3" s="14">
+      <c r="A3" s="12">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="18">
         <v>7</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="16">
         <v>4</v>
       </c>
-      <c r="H3" s="17"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:11" ht="19.95" customHeight="1">
-      <c r="A4" s="14">
-        <v>70</v>
-      </c>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="18">
         <v>1441</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="16">
         <v>677</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="16">
         <v>137</v>
       </c>
     </row>

--- a/大客户订购商品统计表_格式化模板.xlsx
+++ b/大客户订购商品统计表_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B75E6C-A182-461F-838C-5472C0159FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9706EA0-8C36-41ED-AA2D-4865C4FCFE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2064" yWindow="2208" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大客户订购商品统计表" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -139,14 +139,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
@@ -266,23 +258,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -777,7 +769,7 @@
   <cols>
     <col min="1" max="1" width="4.6640625" style="10" customWidth="1"/>
     <col min="2" max="2" width="18.88671875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" style="11" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" style="11" customWidth="1"/>
     <col min="5" max="5" width="4.44140625" style="10" customWidth="1"/>
     <col min="6" max="6" width="6" style="9" bestFit="1" customWidth="1"/>
@@ -840,49 +832,49 @@
       <c r="A3" s="12">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="16">
         <v>7</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="15">
         <v>4</v>
       </c>
-      <c r="H3" s="16"/>
+      <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:11" ht="19.95" customHeight="1">
       <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="16">
         <v>1441</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="15">
         <v>677</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="15">
         <v>137</v>
       </c>
     </row>

--- a/大客户订购商品统计表_格式化模板.xlsx
+++ b/大客户订购商品统计表_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9706EA0-8C36-41ED-AA2D-4865C4FCFE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CD6E65-E6D3-494B-96E7-8F0753E87BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2064" yWindow="2208" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大客户订购商品统计表" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
-    <t>大客户门店下单数量统计表</t>
-  </si>
-  <si>
     <t>序号</t>
   </si>
   <si>
@@ -62,20 +59,24 @@
     <t>-</t>
   </si>
   <si>
-    <t>配送：2026.05.27</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>下单：2026.05.27</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>滨江店</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>东莞凤岗店</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔司家门店下单数量表</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>配送:2026.05.27</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -100,13 +101,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -151,6 +145,12 @@
       <b/>
       <sz val="12"/>
       <color indexed="8"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -225,56 +225,56 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,114 +767,114 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="4.44140625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="4.44140625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="6" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="10.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" style="8" customWidth="1"/>
-    <col min="10" max="10" width="6.88671875" style="8" customWidth="1"/>
-    <col min="11" max="11" width="9" style="8"/>
-    <col min="12" max="16384" width="9" style="9"/>
+    <col min="9" max="9" width="10.33203125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="9" style="7"/>
+    <col min="12" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" ht="22.05" customHeight="1">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="22.05" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+        <v>11</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="24" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>15</v>
+      <c r="G2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="19.95" customHeight="1">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="16">
+      <c r="F3" s="15">
         <v>7</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="14">
         <v>4</v>
       </c>
-      <c r="H3" s="15"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:11" ht="19.95" customHeight="1">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="B4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="15">
         <v>1441</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="14">
         <v>677</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="14">
         <v>137</v>
       </c>
     </row>
@@ -883,7 +883,7 @@
   <mergeCells count="1">
     <mergeCell ref="E1:H1"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="7.8472222222222193E-2" right="0.156944444444444" top="0.156944444444444" bottom="7.8472222222222193E-2" header="0.156944444444444" footer="0.29861111111111099"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
